--- a/lesmateriaal/excel-basis/excel-startbestand.xlsx
+++ b/lesmateriaal/excel-basis/excel-startbestand.xlsx
@@ -432,10 +432,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A18"/>
+  <dimension ref="A1:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="90" customWidth="1" min="1" max="1"/>
+    <col width="92" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -509,14 +509,14 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Blad 3 Verkoop        — cijfers samenvatten</t>
+          <t>Blad 3 Verkoop        — cijfers samenvatten in twee richtingen</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Blad 4 Bestellingen   — het rekenblad laten beslissen</t>
+          <t>Blad 4 Bestellingen   — het rekenblad laten beslissen en daarna tellen</t>
         </is>
       </c>
     </row>
@@ -541,6 +541,23 @@
       <c r="A18" t="inlineStr">
         <is>
           <t>is nog niet af.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Reken nooit iets uit met je rekenmachine om het daarna over te typen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Alles wat je invult begint met een isgelijkteken.</t>
         </is>
       </c>
     </row>
@@ -555,12 +572,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="26" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
   </cols>
@@ -743,10 +760,82 @@
         <v>3.65</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PL-018</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Plint eik 18 mm</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>86</v>
+      </c>
+      <c r="D12" t="n">
+        <v>11.75</v>
+      </c>
+    </row>
     <row r="13">
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Totale voorraadwaarde</t>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>KB-050</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Kabelgoot 5 m</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>64</v>
+      </c>
+      <c r="D13" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SV-025</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Silicone koker</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>245</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.85</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>TG-200</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tegellijm 20 kg</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>118</v>
+      </c>
+      <c r="D15" t="n">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Totaal</t>
         </is>
       </c>
     </row>
@@ -761,13 +850,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -808,6 +898,11 @@
           <t>Verschil</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Verschil in %</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -877,6 +972,36 @@
       </c>
       <c r="B12" t="n">
         <v>5.2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Plint eik 18 mm</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>11.75</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Kabelgoot 5 m</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>16.4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Tegellijm 20 kg</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>13.2</v>
       </c>
     </row>
   </sheetData>
@@ -890,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1030,36 +1155,75 @@
         <v>22600</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Greet Ostyn</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>26800</v>
+      </c>
+      <c r="C10" t="n">
+        <v>25300</v>
+      </c>
+      <c r="D10" t="n">
+        <v>24900</v>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Samenvatting</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Hoogste kwartaaltotaal</t>
-        </is>
+          <t>HansVanacker</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>17450</v>
+      </c>
+      <c r="C11" t="n">
+        <v>18900</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20350</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Laagste kwartaaltotaal</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gemiddeld kwartaaltotaal</t>
+          <t>Totaal per maand</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
+        <is>
+          <t>Samenvatting</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Hoogste kwartaaltotaal</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Laagste kwartaaltotaal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Gemiddeld kwartaaltotaal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Aantal verkopers</t>
         </is>
@@ -1076,7 +1240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1274,17 +1438,91 @@
         <v>1476.8</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>B-2111</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Dakwerken Lievens</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>724.35</v>
+      </c>
+    </row>
     <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>B-2112</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>Klusbedrijf Six</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>398.15</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>B-2113</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tuinaanleg Groen</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>B-2114</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Installatie Vandaele</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>463.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
           <t>Aantal gratis leveringen</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="B18" t="inlineStr">
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Aantal betalende leveringen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
         <is>
           <t>Bedrag van de gratis leveringen</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Bedrag van de betalende leveringen</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1537,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1450,7 +1688,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K-108</t>
+          <t>K-110</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1494,7 +1732,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>K-105</t>
+          <t>K-112</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1516,22 +1754,80 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>K-105</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>K-108</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Renovatie Top</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Deinze</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>K-109</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>K-109</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Betonwerken Callens</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Wervik</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>K-106</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>K-110</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Schilderwerk Bruyneel</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Harelbeke</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
         <is>
           <t>K-108</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Renovatie Top</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Deinze</t>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>K-101</t>
         </is>
       </c>
     </row>
